--- a/data/trans_dic/P02E$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,25</t>
+          <t>1,48; 12,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 14,29</t>
+          <t>3,16; 15,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 21,69</t>
+          <t>5,31; 21,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 12,24</t>
+          <t>2,08; 12,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 10,91</t>
+          <t>2,45; 11,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 26,84</t>
+          <t>12,11; 27,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 9,5</t>
+          <t>2,48; 9,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 10,31</t>
+          <t>3,86; 10,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 21,58</t>
+          <t>11,38; 21,73</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,91</t>
+          <t>1,49; 13,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 8,7</t>
+          <t>1,85; 8,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,78</t>
+          <t>1,25; 10,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,88; 21,12</t>
+          <t>9,2; 21,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,47</t>
+          <t>1,99; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,97</t>
+          <t>3,74; 12,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 16,7</t>
+          <t>7,62; 16,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,84</t>
+          <t>2,68; 7,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,71</t>
+          <t>2,86; 9,3</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 17,81</t>
+          <t>3,07; 17,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 11,36</t>
+          <t>2,07; 11,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,99</t>
+          <t>1,4; 10,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,45</t>
+          <t>0,94; 8,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 14,45</t>
+          <t>4,22; 14,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 18,76</t>
+          <t>4,89; 19,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,84</t>
+          <t>3,11; 10,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 10,84</t>
+          <t>4,28; 11,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,16</t>
+          <t>4,29; 13,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 17,7</t>
+          <t>5,45; 16,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 17,52</t>
+          <t>4,43; 18,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 16,93</t>
+          <t>3,13; 15,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 17,53</t>
+          <t>5,44; 17,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,95</t>
+          <t>6,95; 15,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 10,61</t>
+          <t>2,32; 10,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,36; 14,81</t>
+          <t>6,64; 15,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,3</t>
+          <t>6,85; 14,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,49</t>
+          <t>3,41; 10,31</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,36</t>
+          <t>0,0; 17,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 19,83</t>
+          <t>1,85; 16,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,07</t>
+          <t>0,0; 14,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 17,08</t>
+          <t>4,43; 17,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 14,68</t>
+          <t>3,1; 14,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,01</t>
+          <t>1,2; 11,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 14,66</t>
+          <t>4,78; 14,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,95</t>
+          <t>1,6; 8,11</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 23,84</t>
+          <t>3,31; 21,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 8,52</t>
+          <t>1,08; 9,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,35</t>
+          <t>0,0; 8,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,5</t>
+          <t>1,49; 13,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 13,92</t>
+          <t>3,91; 14,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,59</t>
+          <t>0,95; 5,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,06</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,29; 16,78</t>
+          <t>5,79; 17,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 8,4</t>
+          <t>2,65; 8,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 10,62</t>
+          <t>1,78; 10,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,71</t>
+          <t>1,7; 6,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 19,87</t>
+          <t>8,99; 19,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,53</t>
+          <t>2,32; 6,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,95</t>
+          <t>2,54; 6,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 14,28</t>
+          <t>7,23; 14,33</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 13,86</t>
+          <t>3,97; 13,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,22</t>
+          <t>0,98; 5,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 8,88</t>
+          <t>3,06; 9,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,4</t>
+          <t>2,83; 10,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,74</t>
+          <t>1,56; 5,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,26</t>
+          <t>6,0; 12,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,42</t>
+          <t>3,99; 9,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,71</t>
+          <t>1,87; 5,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,28; 10,07</t>
+          <t>5,34; 9,66</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,39</t>
+          <t>6,35; 10,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,81</t>
+          <t>3,87; 6,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,61; 6,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,68</t>
+          <t>4,85; 7,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,66</t>
+          <t>4,17; 6,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,36</t>
+          <t>7,81; 11,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,26</t>
+          <t>5,69; 8,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,34</t>
+          <t>4,36; 6,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,09</t>
+          <t>6,54; 9,16</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>936; 7936</t>
+          <t>958; 8096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3064; 12707</t>
+          <t>2807; 13448</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4810; 16018</t>
+          <t>3924; 15739</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2139; 12759</t>
+          <t>2169; 13384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4069; 15386</t>
+          <t>3461; 16057</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11043; 26507</t>
+          <t>11959; 27103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4155; 16048</t>
+          <t>4199; 16790</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8248; 23703</t>
+          <t>8879; 24295</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18734; 37240</t>
+          <t>19639; 37496</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1040; 9599</t>
+          <t>1026; 9652</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2088; 11264</t>
+          <t>2395; 11603</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1004; 8617</t>
+          <t>998; 8199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12254; 29143</t>
+          <t>12688; 29114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4123; 15859</t>
+          <t>4230; 16787</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4077; 16044</t>
+          <t>5019; 16411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15840; 34562</t>
+          <t>15770; 34880</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8852; 23363</t>
+          <t>9144; 24530</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6967; 20783</t>
+          <t>6131; 19893</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2126; 12403</t>
+          <t>2138; 11902</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1860; 10621</t>
+          <t>1933; 11151</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>860; 7178</t>
+          <t>840; 6352</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>969; 8892</t>
+          <t>985; 8706</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6472; 20193</t>
+          <t>5898; 19650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4120; 15054</t>
+          <t>3924; 15413</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5046; 17210</t>
+          <t>5441; 19137</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9801; 25293</t>
+          <t>9976; 27238</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5893; 18444</t>
+          <t>6005; 19011</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3934; 15136</t>
+          <t>4658; 14521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5036; 19486</t>
+          <t>4931; 20837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1871; 10023</t>
+          <t>1852; 9446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6673; 20466</t>
+          <t>6349; 20052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12166; 28849</t>
+          <t>12561; 28578</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2352; 12571</t>
+          <t>2751; 12400</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12873; 29967</t>
+          <t>13427; 30688</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19166; 41768</t>
+          <t>20000; 41369</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5726; 18642</t>
+          <t>6068; 18332</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 5302</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1107; 10894</t>
+          <t>1014; 9224</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 6921</t>
+          <t>0; 7649</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4056; 15791</t>
+          <t>4096; 15845</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2586; 12325</t>
+          <t>2602; 12361</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>863; 8402</t>
+          <t>1010; 9396</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7115; 21611</t>
+          <t>7040; 21293</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2322; 12429</t>
+          <t>2501; 12683</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2071; 14191</t>
+          <t>1970; 12990</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>895; 6989</t>
+          <t>887; 7804</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5868</t>
+          <t>0; 5348</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1020; 9352</t>
+          <t>1031; 9398</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6187</t>
+          <t>0; 7166</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5978</t>
+          <t>0; 6156</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4948; 17927</t>
+          <t>5040; 18198</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1843; 10740</t>
+          <t>1828; 10079</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8135</t>
+          <t>0; 8044</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5900; 18714</t>
+          <t>6456; 19391</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5673; 18036</t>
+          <t>5698; 18934</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2223; 13002</t>
+          <t>2175; 13076</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7017</t>
+          <t>0; 6064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4109; 16211</t>
+          <t>4826; 17012</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18522; 40479</t>
+          <t>18309; 38824</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7872; 21817</t>
+          <t>7752; 21877</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12597; 29678</t>
+          <t>12634; 30205</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23789; 46597</t>
+          <t>23588; 46755</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5440; 18734</t>
+          <t>5363; 18407</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2245; 13062</t>
+          <t>2062; 12388</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6155; 20088</t>
+          <t>6922; 21403</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4991; 18521</t>
+          <t>5576; 19702</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6362; 20484</t>
+          <t>5575; 19437</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18781; 39452</t>
+          <t>19307; 40310</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12845; 31301</t>
+          <t>13260; 32187</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10442; 26675</t>
+          <t>10620; 28573</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28930; 55179</t>
+          <t>29247; 52933</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>38959; 65075</t>
+          <t>39746; 66857</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37619; 67032</t>
+          <t>38149; 66076</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27861; 51102</t>
+          <t>27325; 52759</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>46801; 77212</t>
+          <t>48783; 77764</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>63709; 100977</t>
+          <t>63294; 98066</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85700; 126184</t>
+          <t>86790; 125425</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93071; 134732</t>
+          <t>92870; 134030</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>110604; 158601</t>
+          <t>109007; 156063</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>121619; 169745</t>
+          <t>122174; 171046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,5</t>
+          <t>1,46; 12,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 15,12</t>
+          <t>3,14; 14,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 21,31</t>
+          <t>5,51; 21,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,84</t>
+          <t>2,04; 11,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,39</t>
+          <t>2,83; 10,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 27,45</t>
+          <t>11,25; 26,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,93</t>
+          <t>2,5; 10,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,57</t>
+          <t>3,93; 10,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 21,73</t>
+          <t>10,82; 21,89</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,98</t>
+          <t>1,48; 14,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,97</t>
+          <t>2,12; 9,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,26</t>
+          <t>1,26; 10,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 21,1</t>
+          <t>9,23; 21,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,91</t>
+          <t>2,31; 7,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,24</t>
+          <t>3,7; 12,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 16,85</t>
+          <t>8,02; 16,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,18</t>
+          <t>2,59; 7,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 9,3</t>
+          <t>2,89; 9,57</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 17,09</t>
+          <t>4,1; 17,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 11,93</t>
+          <t>2,02; 12,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,61</t>
+          <t>1,44; 12,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,28</t>
+          <t>0,94; 8,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 14,06</t>
+          <t>4,28; 14,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 19,2</t>
+          <t>5,29; 20,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,95</t>
+          <t>2,85; 10,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,68</t>
+          <t>4,2; 11,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,29; 13,57</t>
+          <t>4,29; 13,28</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 16,98</t>
+          <t>5,25; 17,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 18,74</t>
+          <t>4,21; 16,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 15,95</t>
+          <t>3,18; 16,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 17,18</t>
+          <t>6,05; 17,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 15,8</t>
+          <t>6,44; 16,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 10,46</t>
+          <t>1,78; 9,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,17</t>
+          <t>6,67; 14,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,17</t>
+          <t>6,94; 14,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 10,31</t>
+          <t>3,23; 10,47</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,11</t>
+          <t>0,0; 17,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 16,79</t>
+          <t>1,97; 18,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,44</t>
+          <t>0,0; 14,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,43; 17,14</t>
+          <t>4,39; 17,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,73</t>
+          <t>2,79; 14,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,19</t>
+          <t>1,17; 11,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,45</t>
+          <t>5,4; 14,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,11</t>
+          <t>1,45; 7,54</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 21,82</t>
+          <t>3,49; 22,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,51</t>
+          <t>1,06; 9,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,52</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,57</t>
+          <t>1,47; 13,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 14,13</t>
+          <t>3,92; 14,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,24</t>
+          <t>0,99; 5,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,06</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 17,38</t>
+          <t>5,74; 17,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,82</t>
+          <t>2,62; 8,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,68</t>
+          <t>1,77; 10,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,0</t>
+          <t>1,44; 5,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,99; 19,05</t>
+          <t>8,79; 19,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,55</t>
+          <t>2,26; 6,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,06</t>
+          <t>2,47; 5,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 14,33</t>
+          <t>7,15; 13,99</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,97; 13,62</t>
+          <t>4,28; 13,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,9</t>
+          <t>1,04; 6,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 9,46</t>
+          <t>2,67; 8,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,83; 10,0</t>
+          <t>2,78; 9,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,45</t>
+          <t>1,58; 5,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 12,53</t>
+          <t>6,14; 12,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,69</t>
+          <t>3,93; 9,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,04</t>
+          <t>1,99; 4,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,34; 9,66</t>
+          <t>5,5; 9,98</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,68</t>
+          <t>6,14; 10,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,71</t>
+          <t>3,9; 6,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,97</t>
+          <t>3,73; 6,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,73</t>
+          <t>4,87; 7,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,46</t>
+          <t>4,21; 6,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,29</t>
+          <t>7,65; 11,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,21</t>
+          <t>5,68; 8,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,24</t>
+          <t>4,44; 6,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,16</t>
+          <t>6,58; 8,95</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>958; 8096</t>
+          <t>942; 8008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2807; 13448</t>
+          <t>2796; 12700</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3924; 15739</t>
+          <t>4072; 15686</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2169; 13384</t>
+          <t>2129; 12172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3461; 16057</t>
+          <t>3983; 15283</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11959; 27103</t>
+          <t>11104; 26628</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4199; 16790</t>
+          <t>4219; 16916</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8879; 24295</t>
+          <t>9025; 24047</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19639; 37496</t>
+          <t>18666; 37786</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1026; 9652</t>
+          <t>1025; 10009</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2395; 11603</t>
+          <t>2740; 11738</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>998; 8199</t>
+          <t>1009; 8362</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12688; 29114</t>
+          <t>12732; 29844</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4230; 16787</t>
+          <t>4907; 16577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5019; 16411</t>
+          <t>4961; 16198</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15770; 34880</t>
+          <t>16603; 34441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9144; 24530</t>
+          <t>8854; 24016</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6131; 19893</t>
+          <t>6195; 20478</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2138; 11902</t>
+          <t>2857; 12264</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1933; 11151</t>
+          <t>1891; 11511</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>840; 6352</t>
+          <t>860; 7539</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>985; 8706</t>
+          <t>985; 8852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5898; 19650</t>
+          <t>5985; 19563</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3924; 15413</t>
+          <t>4248; 16679</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5441; 19137</t>
+          <t>4975; 17481</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9976; 27238</t>
+          <t>9808; 25821</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6005; 19011</t>
+          <t>6007; 18603</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4658; 14521</t>
+          <t>4489; 15011</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4931; 20837</t>
+          <t>4685; 18824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1852; 9446</t>
+          <t>1885; 9722</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6349; 20052</t>
+          <t>7066; 20016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12561; 28578</t>
+          <t>11644; 29608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2751; 12400</t>
+          <t>2111; 11558</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13427; 30688</t>
+          <t>13482; 29991</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20000; 41369</t>
+          <t>20279; 42646</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6068; 18332</t>
+          <t>5736; 18614</t>
         </is>
       </c>
     </row>
@@ -2513,12 +2513,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5302</t>
+          <t>0; 5473</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1014; 9224</t>
+          <t>1080; 9971</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2528,32 +2528,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 7649</t>
+          <t>0; 7518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4096; 15845</t>
+          <t>4058; 15992</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2602; 12361</t>
+          <t>2345; 11904</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1010; 9396</t>
+          <t>984; 9363</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7040; 21293</t>
+          <t>7964; 21379</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2501; 12683</t>
+          <t>2260; 11785</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1970; 12990</t>
+          <t>2077; 13438</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>887; 7804</t>
+          <t>872; 7525</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5348</t>
+          <t>0; 5479</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1031; 9398</t>
+          <t>1019; 9389</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7166</t>
+          <t>0; 7129</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 6156</t>
+          <t>0; 5906</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5040; 18198</t>
+          <t>5043; 18576</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1828; 10079</t>
+          <t>1895; 10444</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8044</t>
+          <t>0; 8025</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6456; 19391</t>
+          <t>6403; 19589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5698; 18934</t>
+          <t>5631; 19152</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2175; 13076</t>
+          <t>2173; 12996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 6064</t>
+          <t>0; 6839</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4826; 17012</t>
+          <t>4075; 16492</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18309; 38824</t>
+          <t>17910; 39199</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7752; 21877</t>
+          <t>7561; 20989</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12634; 30205</t>
+          <t>12317; 29807</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23588; 46755</t>
+          <t>23313; 45633</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5363; 18407</t>
+          <t>5793; 18017</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2062; 12388</t>
+          <t>2183; 13102</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6922; 21403</t>
+          <t>6037; 20288</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5576; 19702</t>
+          <t>5483; 18391</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5575; 19437</t>
+          <t>5631; 20563</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19307; 40310</t>
+          <t>19768; 41241</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13260; 32187</t>
+          <t>13045; 31790</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10620; 28573</t>
+          <t>11287; 27488</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29247; 52933</t>
+          <t>30152; 54693</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>39746; 66857</t>
+          <t>38436; 66471</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38149; 66076</t>
+          <t>38440; 67796</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27325; 52759</t>
+          <t>28249; 52097</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48783; 77764</t>
+          <t>48958; 79429</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>63294; 98066</t>
+          <t>63874; 100401</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86790; 125425</t>
+          <t>85011; 125404</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92870; 134030</t>
+          <t>92771; 134876</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>109007; 156063</t>
+          <t>111033; 156376</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>122174; 171046</t>
+          <t>122813; 167237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
